--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9C4B7F5-3FC1-4DA0-B8DD-FF6BD6D41D84}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17B8288B-E67C-4826-AC90-1D413A09AB22}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,10 +498,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1400,20 +1396,22 @@
       <c r="A14" s="8">
         <v>46260</v>
       </c>
-      <c r="B14" s="9"/>
+      <c r="B14" s="9">
+        <v>543</v>
+      </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>543</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>897</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17B8288B-E67C-4826-AC90-1D413A09AB22}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E33D4D5-BE28-4E3E-A004-0C7EFFE59E9B}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Booring day</t>
+  </si>
+  <si>
+    <t>Today's day was awsome.</t>
   </si>
 </sst>
 </file>
@@ -498,6 +501,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1397,26 +1404,46 @@
         <v>46260</v>
       </c>
       <c r="B14" s="9">
-        <v>543</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+        <v>390</v>
+      </c>
+      <c r="C14" s="9">
+        <v>100</v>
+      </c>
+      <c r="D14" s="9">
+        <v>130</v>
+      </c>
+      <c r="E14" s="9">
+        <v>160</v>
+      </c>
+      <c r="F14" s="9">
+        <v>350</v>
+      </c>
+      <c r="G14" s="9">
+        <v>7</v>
+      </c>
+      <c r="H14" s="9">
+        <v>80</v>
+      </c>
       <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v>543</v>
+        <v>1210</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v>897</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E33D4D5-BE28-4E3E-A004-0C7EFFE59E9B}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0148953-560B-4643-B4EC-B65261CFCF29}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,9 +217,6 @@
     <t>Feeling good today.</t>
   </si>
   <si>
-    <t>2026-28-29</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -251,6 +248,12 @@
   </si>
   <si>
     <t>Today's day was awsome.</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>practice on sql.</t>
   </si>
 </sst>
 </file>
@@ -1114,13 +1117,13 @@
         <v>56</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1209,7 +1212,7 @@
         <v>55</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>59</v>
@@ -1255,10 +1258,10 @@
         <v>49</v>
       </c>
       <c r="M10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -1295,16 +1298,16 @@
         <v>340</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1350,7 +1353,7 @@
         <v>56</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1387,16 +1390,16 @@
         <v>290</v>
       </c>
       <c r="K13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1439,40 +1442,60 @@
         <v>49</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>46261</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="B15" s="9">
+        <v>480</v>
+      </c>
+      <c r="C15" s="9">
+        <v>80</v>
+      </c>
+      <c r="D15" s="9">
+        <v>300</v>
+      </c>
+      <c r="E15" s="9">
+        <v>180</v>
+      </c>
+      <c r="F15" s="9">
+        <v>200</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>46262</v>
-      </c>
+      <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -1494,9 +1517,7 @@
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>60</v>
-      </c>
+      <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1518,9 +1539,7 @@
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>46264</v>
-      </c>
+      <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1542,9 +1561,7 @@
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>46265</v>
-      </c>
+      <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0148953-560B-4643-B4EC-B65261CFCF29}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E23FD1-5808-4E1B-A59C-F1AE16510E2B}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>practice on sql.</t>
+  </si>
+  <si>
+    <t>learning sql</t>
   </si>
 </sst>
 </file>
@@ -1495,26 +1498,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B16" s="9">
+        <v>460</v>
+      </c>
+      <c r="C16" s="9">
+        <v>70</v>
+      </c>
+      <c r="D16" s="9">
+        <v>200</v>
+      </c>
+      <c r="E16" s="9">
+        <v>100</v>
+      </c>
+      <c r="F16" s="9">
+        <v>150</v>
+      </c>
+      <c r="G16" s="9">
+        <v>3</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E23FD1-5808-4E1B-A59C-F1AE16510E2B}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F074010E-22BE-49EC-9369-4C1DCFA3F05D}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>learning sql</t>
+  </si>
+  <si>
+    <t>Awsome</t>
+  </si>
+  <si>
+    <t>leaning DSA.</t>
   </si>
 </sst>
 </file>
@@ -1544,26 +1550,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B17" s="9">
+        <v>400</v>
+      </c>
+      <c r="C17" s="9">
+        <v>120</v>
+      </c>
+      <c r="D17" s="9">
+        <v>420</v>
+      </c>
+      <c r="E17" s="9">
+        <v>200</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>70</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F074010E-22BE-49EC-9369-4C1DCFA3F05D}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD3A94D-5012-445A-99E1-B9855851D50A}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>leaning DSA.</t>
+  </si>
+  <si>
+    <t>Learning DSA.</t>
   </si>
 </sst>
 </file>
@@ -1596,26 +1599,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B18" s="9">
+        <v>460</v>
+      </c>
+      <c r="C18" s="9">
+        <v>60</v>
+      </c>
+      <c r="D18" s="9">
+        <v>360</v>
+      </c>
+      <c r="E18" s="9">
+        <v>150</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FD3A94D-5012-445A-99E1-B9855851D50A}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB468C9-77F6-4907-A834-352D32C41490}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Learning DSA.</t>
+  </si>
+  <si>
+    <t>Tied day.</t>
   </si>
 </sst>
 </file>
@@ -1645,26 +1648,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="9">
+        <v>380</v>
+      </c>
+      <c r="C19" s="9">
+        <v>90</v>
+      </c>
+      <c r="D19" s="9">
+        <v>200</v>
+      </c>
+      <c r="E19" s="9">
+        <v>70</v>
+      </c>
+      <c r="F19" s="9">
+        <v>200</v>
+      </c>
+      <c r="G19" s="9">
+        <v>4</v>
+      </c>
+      <c r="H19" s="9">
+        <v>70</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>430</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB468C9-77F6-4907-A834-352D32C41490}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5186DF00-3080-4769-9754-9C6DF34E5ACE}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Tied day.</t>
+  </si>
+  <si>
+    <t>Learning sql and python</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1069,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="9">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="G6" s="9">
         <v>7</v>
@@ -1076,11 +1079,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" si="0"/>
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" si="1"/>
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>48</v>
@@ -1694,26 +1697,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+      <c r="A20" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="9">
+        <v>340</v>
+      </c>
+      <c r="C20" s="9">
+        <v>70</v>
+      </c>
+      <c r="D20" s="9">
+        <v>230</v>
+      </c>
+      <c r="E20" s="9">
+        <v>40</v>
+      </c>
+      <c r="F20" s="9">
+        <v>450</v>
+      </c>
+      <c r="G20" s="9">
+        <v>7</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
@@ -10066,7 +10093,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K5:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5186DF00-3080-4769-9754-9C6DF34E5ACE}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D1C216C-F8BE-4B29-945E-93CDBA828935}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Learning sql and python</t>
+  </si>
+  <si>
+    <t>Day was quite good.</t>
   </si>
 </sst>
 </file>
@@ -1743,26 +1746,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="9">
+        <v>370</v>
+      </c>
+      <c r="C21" s="9">
+        <v>80</v>
+      </c>
+      <c r="D21" s="9">
+        <v>280</v>
+      </c>
+      <c r="E21" s="9">
+        <v>70</v>
+      </c>
+      <c r="F21" s="9">
+        <v>450</v>
+      </c>
+      <c r="G21" s="9">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>190</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
@@ -10093,7 +10120,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K5:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D1C216C-F8BE-4B29-945E-93CDBA828935}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DA0CAEB-8C32-4C4E-9803-C1E16EB87000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Day was quite good.</t>
+  </si>
+  <si>
+    <t>Feeling tied .</t>
   </si>
 </sst>
 </file>
@@ -1792,26 +1795,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="9">
+        <v>330</v>
+      </c>
+      <c r="C22" s="9">
+        <v>100</v>
+      </c>
+      <c r="D22" s="9">
+        <v>190</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>200</v>
+      </c>
+      <c r="G22" s="9">
+        <v>4</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>820</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>620</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DA0CAEB-8C32-4C4E-9803-C1E16EB87000}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3D2D4A-AD8F-4689-9E98-78A1AB48DC00}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1841,26 +1841,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="9">
+        <v>390</v>
+      </c>
+      <c r="C23" s="9">
+        <v>90</v>
+      </c>
+      <c r="D23" s="9">
+        <v>160</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>250</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>70</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>480</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3D2D4A-AD8F-4689-9E98-78A1AB48DC00}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF3BC33A-CF03-4F47-BF1B-4138275A3B19}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,9 +232,6 @@
     <t>Felt Sleepy after eating chole bhature.</t>
   </si>
   <si>
-    <t xml:space="preserve"> learning DSA</t>
-  </si>
-  <si>
     <t>Very low</t>
   </si>
   <si>
@@ -262,12 +259,6 @@
     <t>Awsome</t>
   </si>
   <si>
-    <t>leaning DSA.</t>
-  </si>
-  <si>
-    <t>Learning DSA.</t>
-  </si>
-  <si>
     <t>Tied day.</t>
   </si>
   <si>
@@ -278,6 +269,9 @@
   </si>
   <si>
     <t>Feeling tied .</t>
+  </si>
+  <si>
+    <t>Learning Java.</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1371,7 @@
         <v>56</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1414,16 +1408,16 @@
         <v>290</v>
       </c>
       <c r="K13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="N13" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1469,7 +1463,7 @@
         <v>62</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1512,10 +1506,10 @@
         <v>55</v>
       </c>
       <c r="M15" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1561,7 +1555,7 @@
         <v>50</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1598,7 +1592,7 @@
         <v>230</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L17" s="11" t="s">
         <v>49</v>
@@ -1607,7 +1601,7 @@
         <v>62</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1653,7 +1647,7 @@
         <v>62</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1699,7 +1693,7 @@
         <v>56</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1745,7 +1739,7 @@
         <v>56</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1791,7 +1785,7 @@
         <v>50</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1837,7 +1831,7 @@
         <v>56</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1883,30 +1877,54 @@
         <v>50</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="9">
+        <v>430</v>
+      </c>
+      <c r="C24" s="9">
+        <v>80</v>
+      </c>
+      <c r="D24" s="9">
+        <v>410</v>
+      </c>
+      <c r="E24" s="9">
+        <v>190</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>90</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>240</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF3BC33A-CF03-4F47-BF1B-4138275A3B19}"/>
+  <xr:revisionPtr revIDLastSave="273" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC3C5EB-EF3F-4ADD-8021-E09273B9D427}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Learning Java.</t>
+  </si>
+  <si>
+    <t>Learning Java and Sql.</t>
   </si>
 </sst>
 </file>
@@ -1927,26 +1930,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="9">
+        <v>380</v>
+      </c>
+      <c r="C25" s="9">
+        <v>100</v>
+      </c>
+      <c r="D25" s="9">
+        <v>430</v>
+      </c>
+      <c r="E25" s="9">
+        <v>180</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="273" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC3C5EB-EF3F-4ADD-8021-E09273B9D427}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C911B1A2-4279-4235-9E54-EEF871383F96}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,7 +284,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,8 +351,15 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,6 +376,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -399,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -427,6 +440,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1976,26 +1992,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="9">
+        <v>330</v>
+      </c>
+      <c r="C26" s="9">
+        <v>110</v>
+      </c>
+      <c r="D26" s="9">
+        <v>200</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>200</v>
+      </c>
+      <c r="G26" s="9">
+        <v>4</v>
+      </c>
+      <c r="H26" s="9">
+        <v>50</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
@@ -10231,6 +10271,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C911B1A2-4279-4235-9E54-EEF871383F96}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD4A02D-843F-4620-A79E-44AAA80A9CA3}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -276,6 +276,9 @@
   <si>
     <t>Learning Java and Sql.</t>
   </si>
+  <si>
+    <t>Learning sql.</t>
+  </si>
 </sst>
 </file>
 
@@ -438,11 +441,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,56 +933,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <v>12605028</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
@@ -2033,31 +2036,55 @@
       <c r="M26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="15" t="s">
+      <c r="N26" s="13" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="A27" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="9">
+        <v>350</v>
+      </c>
+      <c r="C27" s="9">
+        <v>80</v>
+      </c>
+      <c r="D27" s="9">
+        <v>240</v>
+      </c>
+      <c r="E27" s="9">
+        <v>80</v>
+      </c>
+      <c r="F27" s="9">
+        <v>450</v>
+      </c>
+      <c r="G27" s="9">
+        <v>7</v>
+      </c>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>240</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD4A02D-843F-4620-A79E-44AAA80A9CA3}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7C4AE07-74CC-4AEF-ABBB-E9727683E4C0}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Learning sql.</t>
+  </si>
+  <si>
+    <t>Attending classes and Preparing for hackathon.</t>
   </si>
 </sst>
 </file>
@@ -2086,27 +2089,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+    <row r="28" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B28" s="9">
+        <v>310</v>
+      </c>
+      <c r="C28" s="9">
+        <v>80</v>
+      </c>
+      <c r="D28" s="9">
+        <v>180</v>
+      </c>
+      <c r="E28" s="9">
+        <v>110</v>
+      </c>
+      <c r="F28" s="9">
+        <v>450</v>
+      </c>
+      <c r="G28" s="9">
+        <v>7</v>
+      </c>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7C4AE07-74CC-4AEF-ABBB-E9727683E4C0}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E65F6BB-458A-4ADE-A8F1-E24D260BA1D2}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Attending classes and Preparing for hackathon.</t>
+  </si>
+  <si>
+    <t>Learning a lot of skills and technology in hackathon.</t>
   </si>
 </sst>
 </file>
@@ -2091,7 +2094,7 @@
     </row>
     <row r="28" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="9">
         <v>310</v>
@@ -2135,27 +2138,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+    <row r="29" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="9">
+        <v>280</v>
+      </c>
+      <c r="C29" s="9">
+        <v>110</v>
+      </c>
+      <c r="D29" s="9">
+        <v>490</v>
+      </c>
+      <c r="E29" s="9">
+        <v>210</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E65F6BB-458A-4ADE-A8F1-E24D260BA1D2}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF51E768-718B-4291-963C-B11112A1E7CA}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2184,27 +2184,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+    <row r="30" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="9">
+        <v>310</v>
+      </c>
+      <c r="C30" s="9">
+        <v>90</v>
+      </c>
+      <c r="D30" s="9">
+        <v>210</v>
+      </c>
+      <c r="E30" s="9">
+        <v>390</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF51E768-718B-4291-963C-B11112A1E7CA}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA5EA444-5B58-4321-BA73-B763440B9226}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Learning a lot of skills and technology in hackathon.</t>
+  </si>
+  <si>
+    <t>Learning Aptitude.</t>
   </si>
 </sst>
 </file>
@@ -2231,26 +2234,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="9">
+        <v>380</v>
+      </c>
+      <c r="C31" s="9">
+        <v>70</v>
+      </c>
+      <c r="D31" s="9">
+        <v>450</v>
+      </c>
+      <c r="E31" s="9">
+        <v>80</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>50</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA5EA444-5B58-4321-BA73-B763440B9226}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2C9E254-EA44-426E-BE32-A138CC596B3C}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Learning Aptitude.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2280,26 +2286,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+      <c r="A32" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="9">
+        <v>410</v>
+      </c>
+      <c r="C32" s="9">
+        <v>65</v>
+      </c>
+      <c r="D32" s="9">
+        <v>510</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>985</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>455</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2C9E254-EA44-426E-BE32-A138CC596B3C}"/>
+  <xr:revisionPtr revIDLastSave="385" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B1BB2C-5FD6-4233-8028-27B4B79593F3}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Preparing for CA.</t>
   </si>
 </sst>
 </file>
@@ -2332,26 +2335,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="9">
+        <v>390</v>
+      </c>
+      <c r="C33" s="9">
+        <v>70</v>
+      </c>
+      <c r="D33" s="9">
+        <v>270</v>
+      </c>
+      <c r="E33" s="9">
+        <v>80</v>
+      </c>
+      <c r="F33" s="9">
+        <v>200</v>
+      </c>
+      <c r="G33" s="9">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9">
+        <v>30</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8B1BB2C-5FD6-4233-8028-27B4B79593F3}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62B5986-EC6B-455A-B7D9-9545723B448E}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Preparing for CA.</t>
+  </si>
+  <si>
+    <t>A day with full hectic.</t>
   </si>
 </sst>
 </file>
@@ -2381,26 +2384,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="A34" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="9">
+        <v>470</v>
+      </c>
+      <c r="C34" s="9">
+        <v>80</v>
+      </c>
+      <c r="D34" s="9">
+        <v>310</v>
+      </c>
+      <c r="E34" s="9">
+        <v>130</v>
+      </c>
+      <c r="F34" s="9">
+        <v>250</v>
+      </c>
+      <c r="G34" s="9">
+        <v>5</v>
+      </c>
+      <c r="H34" s="9">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62B5986-EC6B-455A-B7D9-9545723B448E}"/>
+  <xr:revisionPtr revIDLastSave="409" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00236B63-7F29-4A17-9016-360059DA7B6F}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2430,26 +2430,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="9">
+        <v>510</v>
+      </c>
+      <c r="C35" s="9">
+        <v>70</v>
+      </c>
+      <c r="D35" s="9">
+        <v>200</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>350</v>
+      </c>
+      <c r="G35" s="9">
+        <v>7</v>
+      </c>
+      <c r="H35" s="9">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="409" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00236B63-7F29-4A17-9016-360059DA7B6F}"/>
+  <xr:revisionPtr revIDLastSave="421" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{558251A8-10DE-47EA-9793-031C07FDCD6D}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>A day with full hectic.</t>
+  </si>
+  <si>
+    <t>HIgh</t>
   </si>
 </sst>
 </file>
@@ -2476,26 +2479,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="A36" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="9">
+        <v>480</v>
+      </c>
+      <c r="C36" s="9">
+        <v>80</v>
+      </c>
+      <c r="D36" s="9">
+        <v>310</v>
+      </c>
+      <c r="E36" s="9">
+        <v>30</v>
+      </c>
+      <c r="F36" s="9">
+        <v>200</v>
+      </c>
+      <c r="G36" s="9">
+        <v>4</v>
+      </c>
+      <c r="H36" s="9">
+        <v>80</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <v>260</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="421" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{558251A8-10DE-47EA-9793-031C07FDCD6D}"/>
+  <xr:revisionPtr revIDLastSave="433" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3936635A-0C90-44C8-8B8C-B830C9FE0B1D}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>HIgh</t>
+  </si>
+  <si>
+    <t>Learning Aptitude and Preparing for CA.</t>
   </si>
 </sst>
 </file>
@@ -2524,27 +2527,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+    <row r="37" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="9">
+        <v>380</v>
+      </c>
+      <c r="C37" s="9">
+        <v>110</v>
+      </c>
+      <c r="D37" s="9">
+        <v>420</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>120</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3936635A-0C90-44C8-8B8C-B830C9FE0B1D}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1832950-DB66-4F0B-BFF9-D3AB2D13919F}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>Learning Aptitude and Preparing for CA.</t>
+  </si>
+  <si>
+    <t>Learning DBMS.</t>
   </si>
 </sst>
 </file>
@@ -2574,26 +2577,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+      <c r="A38" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="9">
+        <v>430</v>
+      </c>
+      <c r="C38" s="9">
+        <v>150</v>
+      </c>
+      <c r="D38" s="9">
+        <v>320</v>
+      </c>
+      <c r="E38" s="9">
+        <v>110</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>50</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="447" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1832950-DB66-4F0B-BFF9-D3AB2D13919F}"/>
+  <xr:revisionPtr revIDLastSave="462" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A713D28-36D8-42B3-B632-C0233D0F1AD5}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Learning DBMS.</t>
+  </si>
+  <si>
+    <t>Learning DSA.S</t>
   </si>
 </sst>
 </file>
@@ -2623,26 +2626,49 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="A39" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="9">
+        <v>370</v>
+      </c>
+      <c r="C39" s="9">
+        <v>110</v>
+      </c>
+      <c r="D39" s="9">
+        <v>540</v>
+      </c>
+      <c r="E39" s="9">
+        <v>370</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>130</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>1520</v>
+      </c>
+      <c r="J39" s="10">
+        <v>380</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="462" documentId="8_{856E8336-3697-4507-ADBA-F161EE74249F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A713D28-36D8-42B3-B632-C0233D0F1AD5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,7 +310,10 @@
     <t>Learning DBMS.</t>
   </si>
   <si>
-    <t>Learning DSA.S</t>
+    <t>Learning DSA.</t>
+  </si>
+  <si>
+    <t>A day with full of Stress.</t>
   </si>
 </sst>
 </file>
@@ -577,10 +580,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2671,26 +2670,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+      <c r="A40" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="9">
+        <v>310</v>
+      </c>
+      <c r="C40" s="9">
+        <v>150</v>
+      </c>
+      <c r="D40" s="9">
+        <v>230</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>200</v>
+      </c>
+      <c r="G40" s="9">
+        <v>4</v>
+      </c>
+      <c r="H40" s="9">
+        <v>50</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D74B3F5-29E7-4349-9936-BC642B323F8F}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>A day with full of Stress.</t>
+  </si>
+  <si>
+    <t>Feeling tied.</t>
   </si>
 </sst>
 </file>
@@ -2716,26 +2719,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="9">
+        <v>490</v>
+      </c>
+      <c r="C41" s="9">
+        <v>110</v>
+      </c>
+      <c r="D41" s="9">
+        <v>130</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
+        <v>450</v>
+      </c>
+      <c r="G41" s="9">
+        <v>7</v>
+      </c>
+      <c r="H41" s="9">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>260</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D74B3F5-29E7-4349-9936-BC642B323F8F}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5015511F-3891-4D8D-97F2-05DEC5CC7E58}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,16 +202,10 @@
     <t>MCA/D1P2632</t>
   </si>
   <si>
-    <t>satisfied</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
     <t>Feeling tied after classes.</t>
-  </si>
-  <si>
-    <t>Average</t>
   </si>
   <si>
     <t>Feeling good today.</t>
@@ -232,31 +226,16 @@
     <t>Felt Sleepy after eating chole bhature.</t>
   </si>
   <si>
-    <t>Very low</t>
-  </si>
-  <si>
-    <t>not satisfied</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
     <t>Booring day</t>
   </si>
   <si>
     <t>Today's day was awsome.</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
     <t>practice on sql.</t>
   </si>
   <si>
     <t>learning sql</t>
-  </si>
-  <si>
-    <t>Awsome</t>
   </si>
   <si>
     <t>Tied day.</t>
@@ -301,9 +280,6 @@
     <t>A day with full hectic.</t>
   </si>
   <si>
-    <t>HIgh</t>
-  </si>
-  <si>
     <t>Learning Aptitude and Preparing for CA.</t>
   </si>
   <si>
@@ -316,7 +292,13 @@
     <t>A day with full of Stress.</t>
   </si>
   <si>
-    <t>Feeling tied.</t>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Feeling tied all day.</t>
+  </si>
+  <si>
+    <t>Making python on My data my story.</t>
   </si>
 </sst>
 </file>
@@ -394,9 +376,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -422,7 +403,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -581,6 +562,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -953,7 +938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N399"/>
+  <dimension ref="A1:N397"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1089,24 +1074,24 @@
         <v>60</v>
       </c>
       <c r="I5" s="10">
-        <f t="shared" ref="I5:I67" si="0">IF(SUM(B5:F5,H5)=0,"",SUM(B5:F5,H5))</f>
+        <f t="shared" ref="I5:I65" si="0">IF(SUM(B5:F5,H5)=0,"",SUM(B5:F5,H5))</f>
         <v>1340</v>
       </c>
       <c r="J5" s="10">
-        <f t="shared" ref="J5:J67" si="1">IF(I5="","",1440-I5)</f>
+        <f t="shared" ref="J5:J65" si="1">IF(I5="","",1440-I5)</f>
         <v>100</v>
       </c>
       <c r="K5" s="11" t="s">
         <v>58</v>
       </c>
       <c r="L5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1152,7 +1137,7 @@
         <v>50</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1189,16 +1174,16 @@
         <v>170</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1238,7 +1223,7 @@
         <v>48</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>50</v>
@@ -1281,16 +1266,16 @@
         <v>10</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -1333,10 +1318,10 @@
         <v>49</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -1373,16 +1358,16 @@
         <v>340</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="M11" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1422,13 +1407,13 @@
         <v>58</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1465,16 +1450,16 @@
         <v>290</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1517,10 +1502,10 @@
         <v>49</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1560,13 +1545,13 @@
         <v>58</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1606,13 +1591,13 @@
         <v>48</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1649,16 +1634,16 @@
         <v>230</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="L17" s="11" t="s">
         <v>49</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1701,10 +1686,10 @@
         <v>49</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1744,13 +1729,13 @@
         <v>58</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1787,16 +1772,16 @@
         <v>310</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1842,7 +1827,7 @@
         <v>50</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1882,13 +1867,13 @@
         <v>58</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1934,7 +1919,7 @@
         <v>50</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1977,10 +1962,10 @@
         <v>49</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2026,7 +2011,7 @@
         <v>50</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2066,13 +2051,13 @@
         <v>58</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2118,7 +2103,7 @@
         <v>50</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -2164,7 +2149,7 @@
         <v>50</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -2207,10 +2192,10 @@
         <v>49</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -2253,10 +2238,10 @@
         <v>49</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2296,13 +2281,13 @@
         <v>58</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2339,16 +2324,16 @@
         <v>455</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2388,13 +2373,13 @@
         <v>58</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2437,10 +2422,10 @@
         <v>49</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2480,13 +2465,13 @@
         <v>58</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M35" s="11" t="s">
         <v>50</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2529,10 +2514,10 @@
         <v>49</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
@@ -2578,7 +2563,7 @@
         <v>50</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2615,16 +2600,16 @@
         <v>380</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2666,10 +2651,10 @@
         <v>49</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2709,13 +2694,13 @@
         <v>58</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2723,13 +2708,13 @@
         <v>46287</v>
       </c>
       <c r="B41" s="9">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C41" s="9">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D41" s="9">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="E41" s="9">
         <v>0</v>
@@ -2745,46 +2730,70 @@
       </c>
       <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v>1180</v>
+        <v>1230</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="K41" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B42" s="9">
+        <v>320</v>
+      </c>
+      <c r="C42" s="9">
+        <v>90</v>
+      </c>
+      <c r="D42" s="9">
+        <v>360</v>
+      </c>
+      <c r="E42" s="9">
+        <v>290</v>
+      </c>
+      <c r="F42" s="9">
+        <v>300</v>
+      </c>
+      <c r="G42" s="9">
+        <v>6</v>
+      </c>
+      <c r="H42" s="9">
+        <v>0</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="0"/>
+        <v>1360</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K42" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="M41" s="11" t="s">
+      <c r="L42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M42" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N41" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+      <c r="N42" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
@@ -3302,11 +3311,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I66:I129" si="2">IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J66:J129" si="3">IF(I66="","",1440-I66)</f>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3324,11 +3333,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -3346,11 +3355,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" ref="I68:I131" si="2">IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" ref="J68:J131" si="3">IF(I68="","",1440-I68)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -4710,11 +4719,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I130:I193" si="4">IF(SUM(B130:F130,H130)=0,"",SUM(B130:F130,H130))</f>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J130:J193" si="5">IF(I130="","",1440-I130)</f>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4732,11 +4741,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4754,11 +4763,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" ref="I132:I195" si="4">IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" ref="J132:J195" si="5">IF(I132="","",1440-I132)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -6118,11 +6127,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I194:I257" si="6">IF(SUM(B194:F194,H194)=0,"",SUM(B194:F194,H194))</f>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J194:J257" si="7">IF(I194="","",1440-I194)</f>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6140,11 +6149,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6162,11 +6171,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" ref="I196:I259" si="6">IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" ref="J196:J259" si="7">IF(I196="","",1440-I196)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -7526,11 +7535,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I258:I321" si="8">IF(SUM(B258:F258,H258)=0,"",SUM(B258:F258,H258))</f>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J258:J321" si="9">IF(I258="","",1440-I258)</f>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7548,11 +7557,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7570,11 +7579,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" ref="I260:I323" si="8">IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" ref="J260:J323" si="9">IF(I260="","",1440-I260)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -8934,11 +8943,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I322:I385" si="10">IF(SUM(B322:F322,H322)=0,"",SUM(B322:F322,H322))</f>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J322:J385" si="11">IF(I322="","",1440-I322)</f>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8956,11 +8965,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8978,11 +8987,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" ref="I324:I387" si="10">IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" ref="J324:J387" si="11">IF(I324="","",1440-I324)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -10342,11 +10351,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I386:I397" si="12">IF(SUM(B386:F386,H386)=0,"",SUM(B386:F386,H386))</f>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J386:J397" si="13">IF(I386="","",1440-I386)</f>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10364,11 +10373,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10386,11 +10395,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" ref="I388:I399" si="12">IF(SUM(B388:F388,H388)=0,"",SUM(B388:F388,H388))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" ref="J388:J399" si="13">IF(I388="","",1440-I388)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10596,50 +10605,6 @@
       <c r="M397" s="11"/>
       <c r="N397" s="12"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="8"/>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="11"/>
-      <c r="L398" s="11"/>
-      <c r="M398" s="11"/>
-      <c r="N398" s="12"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="8"/>
-      <c r="B399" s="9"/>
-      <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="F399" s="9"/>
-      <c r="G399" s="9"/>
-      <c r="H399" s="9"/>
-      <c r="I399" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="11"/>
-      <c r="L399" s="11"/>
-      <c r="M399" s="11"/>
-      <c r="N399" s="12"/>
-    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:N1"/>
@@ -10648,21 +10613,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J399">
+  <conditionalFormatting sqref="J5:J397">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K5:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K5:K397" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L5:L399" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L5:L397" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M5:M399" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M5:M397" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5015511F-3891-4D8D-97F2-05DEC5CC7E58}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{586F6D98-B725-4902-AF6F-B9BDDBF09B5A}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,7 +298,10 @@
     <t>Feeling tied all day.</t>
   </si>
   <si>
-    <t>Making python on My data my story.</t>
+    <t>Making project on My data my story.</t>
+  </si>
+  <si>
+    <t>Making python project on My data my story.</t>
   </si>
 </sst>
 </file>
@@ -2795,27 +2798,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+    <row r="43" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B43" s="9">
+        <v>360</v>
+      </c>
+      <c r="C43" s="9">
+        <v>110</v>
+      </c>
+      <c r="D43" s="9">
+        <v>410</v>
+      </c>
+      <c r="E43" s="9">
+        <v>90</v>
+      </c>
+      <c r="F43" s="9">
+        <v>150</v>
+      </c>
+      <c r="G43" s="9">
+        <v>3</v>
+      </c>
+      <c r="H43" s="9">
+        <v>70</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+        <v>250</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{A3098B77-BADD-4521-B881-41482C8E8132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{586F6D98-B725-4902-AF6F-B9BDDBF09B5A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -303,6 +303,9 @@
   <si>
     <t>Making python project on My data my story.</t>
   </si>
+  <si>
+    <t>Study for Mid term.</t>
+  </si>
 </sst>
 </file>
 
@@ -567,10 +570,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2845,26 +2844,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="A44" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B44" s="9">
+        <v>350</v>
+      </c>
+      <c r="C44" s="9">
+        <v>130</v>
+      </c>
+      <c r="D44" s="9">
+        <v>350</v>
+      </c>
+      <c r="E44" s="9">
+        <v>130</v>
+      </c>
+      <c r="F44" s="9">
+        <v>200</v>
+      </c>
+      <c r="G44" s="9">
+        <v>4</v>
+      </c>
+      <c r="H44" s="9">
+        <v>90</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+        <v>190</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{923B8FCD-D9B3-471F-9751-E4CB05C72033}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -306,6 +306,21 @@
   <si>
     <t>Study for Mid term.</t>
   </si>
+  <si>
+    <t>Average day.</t>
+  </si>
+  <si>
+    <t>Stressed day.</t>
+  </si>
+  <si>
+    <t>Going delhi.</t>
+  </si>
+  <si>
+    <t>Exploring delhi.</t>
+  </si>
+  <si>
+    <t>Expending all day in train.</t>
+  </si>
 </sst>
 </file>
 
@@ -570,6 +585,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2890,114 +2909,234 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="A45" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B45" s="9">
+        <v>120</v>
+      </c>
+      <c r="C45" s="9">
+        <v>130</v>
+      </c>
+      <c r="D45" s="9">
+        <v>240</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
+        <v>100</v>
+      </c>
+      <c r="G45" s="9">
+        <v>2</v>
+      </c>
+      <c r="H45" s="9">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>590</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+        <v>850</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+      <c r="A46" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B46" s="9">
+        <v>30</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>80</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>110</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
+        <v>1330</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+      <c r="A47" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B47" s="9">
+        <v>240</v>
+      </c>
+      <c r="C47" s="9">
+        <v>120</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>110</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>470</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+        <v>970</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="A48" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B48" s="9">
+        <v>450</v>
+      </c>
+      <c r="C48" s="9">
+        <v>180</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>160</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>790</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+        <v>650</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+      <c r="A49" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B49" s="9">
+        <v>550</v>
+      </c>
+      <c r="C49" s="9">
+        <v>190</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>180</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
+        <v>520</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{923B8FCD-D9B3-471F-9751-E4CB05C72033}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6240D823-5233-4597-B5E2-108B9D419DA6}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,7 +319,10 @@
     <t>Exploring delhi.</t>
   </si>
   <si>
-    <t>Expending all day in train.</t>
+    <t>Spending all day in train.</t>
+  </si>
+  <si>
+    <t>A day with full of travelling.</t>
   </si>
 </sst>
 </file>
@@ -585,10 +588,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3139,26 +3138,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+      <c r="A50" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B50" s="9">
+        <v>460</v>
+      </c>
+      <c r="C50" s="9">
+        <v>180</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>160</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6240D823-5233-4597-B5E2-108B9D419DA6}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B6AE34-2D82-4200-9F10-06A2DBB1382B}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -324,6 +324,9 @@
   <si>
     <t>A day with full of travelling.</t>
   </si>
+  <si>
+    <t>Spending a joyfull day my family.</t>
+  </si>
 </sst>
 </file>
 
@@ -588,6 +591,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3184,26 +3191,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+      <c r="A51" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B51" s="9">
+        <v>480</v>
+      </c>
+      <c r="C51" s="9">
+        <v>220</v>
+      </c>
+      <c r="D51" s="9">
+        <v>120</v>
+      </c>
+      <c r="E51" s="9">
+        <v>50</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>180</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B6AE34-2D82-4200-9F10-06A2DBB1382B}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB5341C8-402E-4C43-A173-4610A41BEA6A}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Spending a joyfull day my family.</t>
+  </si>
+  <si>
+    <t>Normal day.</t>
   </si>
 </sst>
 </file>
@@ -3237,26 +3240,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+      <c r="A52" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B52" s="9">
+        <v>370</v>
+      </c>
+      <c r="C52" s="9">
+        <v>170</v>
+      </c>
+      <c r="D52" s="9">
+        <v>250</v>
+      </c>
+      <c r="E52" s="9">
+        <v>80</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>150</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB5341C8-402E-4C43-A173-4610A41BEA6A}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6299A8EA-36C2-4051-A8F4-58A27A949DCE}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3286,26 +3286,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+      <c r="A53" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B53" s="9">
+        <v>430</v>
+      </c>
+      <c r="C53" s="9">
+        <v>180</v>
+      </c>
+      <c r="D53" s="9">
+        <v>320</v>
+      </c>
+      <c r="E53" s="9">
+        <v>120</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>100</v>
+      </c>
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
+        <v>290</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6299A8EA-36C2-4051-A8F4-58A27A949DCE}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C78BA656-14C5-44E0-A45E-502CE45DE394}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Normal day.</t>
+  </si>
+  <si>
+    <t>Travelling whole day in train.</t>
   </si>
 </sst>
 </file>
@@ -3332,26 +3335,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+      <c r="A54" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B54" s="9">
+        <v>450</v>
+      </c>
+      <c r="C54" s="9">
+        <v>150</v>
+      </c>
+      <c r="D54" s="9">
+        <v>210</v>
+      </c>
+      <c r="E54" s="9">
+        <v>70</v>
+      </c>
+      <c r="F54" s="9">
+        <v>200</v>
+      </c>
+      <c r="G54" s="9">
+        <v>4</v>
+      </c>
+      <c r="H54" s="9">
+        <v>70</v>
+      </c>
+      <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
+        <v>290</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C78BA656-14C5-44E0-A45E-502CE45DE394}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A448942-276E-4F9C-81E2-F63AC8EA4A99}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Travelling whole day in train.</t>
+  </si>
+  <si>
+    <t>Going to college.</t>
   </si>
 </sst>
 </file>
@@ -3381,26 +3384,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+      <c r="A55" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B55" s="9">
+        <v>360</v>
+      </c>
+      <c r="C55" s="9">
+        <v>150</v>
+      </c>
+      <c r="D55" s="9">
+        <v>240</v>
+      </c>
+      <c r="E55" s="9">
+        <v>120</v>
+      </c>
+      <c r="F55" s="9">
+        <v>350</v>
+      </c>
+      <c r="G55" s="9">
+        <v>7</v>
+      </c>
+      <c r="H55" s="9">
+        <v>50</v>
+      </c>
+      <c r="I55" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J55" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A448942-276E-4F9C-81E2-F63AC8EA4A99}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F10EBA-E849-446B-81D3-6ACD0BD2F5FB}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -336,6 +336,12 @@
   <si>
     <t>Going to college.</t>
   </si>
+  <si>
+    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample - overwrite it. Rows 2-3: fill your details.</t>
+  </si>
+  <si>
+    <t>Preparing for Midterm.</t>
+  </si>
 </sst>
 </file>
 
@@ -344,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +423,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -471,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -500,8 +512,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N397"/>
+  <dimension ref="A1:N398"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -989,2378 +1003,2343 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12605028</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>46251</v>
-      </c>
-      <c r="B5" s="9">
-        <v>380</v>
-      </c>
-      <c r="C5" s="9">
-        <v>60</v>
-      </c>
-      <c r="D5" s="9">
-        <v>360</v>
-      </c>
-      <c r="E5" s="9">
-        <v>120</v>
-      </c>
-      <c r="F5" s="9">
-        <v>360</v>
-      </c>
-      <c r="G5" s="9">
-        <v>6</v>
-      </c>
-      <c r="H5" s="9">
-        <v>60</v>
-      </c>
-      <c r="I5" s="10">
-        <f t="shared" ref="I5:I65" si="0">IF(SUM(B5:F5,H5)=0,"",SUM(B5:F5,H5))</f>
-        <v>1340</v>
-      </c>
-      <c r="J5" s="10">
-        <f t="shared" ref="J5:J65" si="1">IF(I5="","",1440-I5)</f>
-        <v>100</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C6" s="9">
         <v>60</v>
       </c>
       <c r="D6" s="9">
+        <v>360</v>
+      </c>
+      <c r="E6" s="9">
+        <v>120</v>
+      </c>
+      <c r="F6" s="9">
+        <v>360</v>
+      </c>
+      <c r="G6" s="9">
+        <v>6</v>
+      </c>
+      <c r="H6" s="9">
+        <v>60</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" ref="I6:I66" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1340</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" ref="J6:J66" si="1">IF(I6="","",1440-I6)</f>
+        <v>100</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
+        <v>360</v>
+      </c>
+      <c r="C7" s="9">
+        <v>60</v>
+      </c>
+      <c r="D7" s="9">
         <v>300</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E7" s="9">
         <v>60</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F7" s="9">
         <v>450</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G7" s="9">
         <v>7</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H7" s="9">
         <v>70</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I7" s="10">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J7" s="10">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
         <v>46253</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B8" s="9">
         <v>400</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C8" s="9">
         <v>90</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D8" s="9">
         <v>240</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E8" s="9">
         <v>120</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F8" s="9">
         <v>360</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G8" s="9">
         <v>6</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H8" s="9">
         <v>60</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I8" s="10">
         <f t="shared" si="0"/>
         <v>1270</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M8" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N8" s="12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>46254</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B9" s="9">
         <v>430</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C9" s="9">
         <v>100</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D9" s="9">
         <v>360</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E9" s="9">
         <v>60</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F9" s="9">
         <v>200</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G9" s="9">
         <v>4</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H9" s="9">
         <v>130</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
         <v>1280</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N9" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
         <v>46255</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B10" s="9">
         <v>330</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C10" s="9">
         <v>120</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D10" s="9">
         <v>420</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E10" s="9">
         <v>190</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F10" s="9">
         <v>200</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G10" s="9">
         <v>4</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H10" s="9">
         <v>170</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
         <v>1430</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N10" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+    <row r="11" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>46256</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B11" s="9">
         <v>380</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C11" s="9">
         <v>60</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D11" s="9">
         <v>420</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E11" s="9">
         <v>250</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F11" s="9">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H11" s="9">
         <v>50</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N11" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    <row r="12" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
         <v>46257</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B12" s="9">
         <v>300</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C12" s="9">
         <v>80</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D12" s="9">
         <v>400</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E12" s="9">
         <v>300</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F12" s="9">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G12" s="9">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H12" s="9">
         <v>20</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N12" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>46258</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B13" s="9">
         <v>400</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C13" s="9">
         <v>90</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D13" s="9">
         <v>50</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E13" s="9">
         <v>450</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F13" s="9">
         <v>200</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G13" s="9">
         <v>4</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H13" s="9">
         <v>60</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
         <v>1250</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K13" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="12" t="s">
+      <c r="N13" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
         <v>46259</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B14" s="9">
         <v>420</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C14" s="9">
         <v>110</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D14" s="9">
         <v>120</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E14" s="9">
         <v>50</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F14" s="9">
         <v>350</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G14" s="9">
         <v>7</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H14" s="9">
         <v>100</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
         <v>1150</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
         <v>290</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N14" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>46260</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B15" s="9">
         <v>390</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C15" s="9">
         <v>100</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D15" s="9">
         <v>130</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E15" s="9">
         <v>160</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F15" s="9">
         <v>350</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G15" s="9">
         <v>7</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H15" s="9">
         <v>80</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L15" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N14" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
         <v>46261</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B16" s="9">
         <v>480</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C16" s="9">
         <v>80</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D16" s="9">
         <v>300</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E16" s="9">
         <v>180</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F16" s="9">
         <v>200</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G16" s="9">
         <v>4</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H16" s="9">
         <v>0</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
         <v>1240</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="M16" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N15" s="12" t="s">
+      <c r="N16" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
         <v>46262</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B17" s="9">
         <v>460</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C17" s="9">
         <v>70</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D17" s="9">
         <v>200</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E17" s="9">
         <v>100</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F17" s="9">
         <v>150</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G17" s="9">
         <v>3</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H17" s="9">
         <v>0</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N16" s="12" t="s">
+      <c r="N17" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
         <v>46263</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B18" s="9">
         <v>400</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C18" s="9">
         <v>120</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D18" s="9">
         <v>420</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E18" s="9">
         <v>200</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F18" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G18" s="9">
         <v>0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H18" s="9">
         <v>70</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="12" t="s">
+      <c r="N18" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>46264</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B19" s="9">
         <v>460</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C19" s="9">
         <v>60</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D19" s="9">
         <v>360</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E19" s="9">
         <v>150</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F19" s="9">
         <v>0</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G19" s="9">
         <v>0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H19" s="9">
         <v>0</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="M19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="12" t="s">
+      <c r="N19" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
         <v>46265</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B20" s="9">
         <v>380</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C20" s="9">
         <v>90</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D20" s="9">
         <v>200</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E20" s="9">
         <v>70</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F20" s="9">
         <v>200</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G20" s="9">
         <v>4</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H20" s="9">
         <v>70</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L20" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="12" t="s">
+      <c r="N20" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
         <v>46266</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B21" s="9">
         <v>340</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C21" s="9">
         <v>70</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D21" s="9">
         <v>230</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E21" s="9">
         <v>40</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F21" s="9">
         <v>450</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G21" s="9">
         <v>7</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H21" s="9">
         <v>0</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="M21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N20" s="12" t="s">
+      <c r="N21" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
         <v>46267</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B22" s="9">
         <v>370</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C22" s="9">
         <v>80</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D22" s="9">
         <v>280</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E22" s="9">
         <v>70</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F22" s="9">
         <v>450</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G22" s="9">
         <v>7</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H22" s="9">
         <v>0</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
         <v>1250</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="M22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N21" s="12" t="s">
+      <c r="N22" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
         <v>46268</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B23" s="9">
         <v>330</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C23" s="9">
         <v>100</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D23" s="9">
         <v>190</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E23" s="9">
         <v>0</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F23" s="9">
         <v>200</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G23" s="9">
         <v>4</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H23" s="9">
         <v>0</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
         <v>620</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="M23" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="N23" s="12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
         <v>46269</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B24" s="9">
         <v>390</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C24" s="9">
         <v>90</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D24" s="9">
         <v>160</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E24" s="9">
         <v>0</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F24" s="9">
         <v>250</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G24" s="9">
         <v>5</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H24" s="9">
         <v>70</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L24" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N23" s="12" t="s">
+      <c r="N24" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
         <v>46270</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B25" s="9">
         <v>430</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C25" s="9">
         <v>80</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D25" s="9">
         <v>410</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E25" s="9">
         <v>190</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F25" s="9">
         <v>0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G25" s="9">
         <v>0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H25" s="9">
         <v>90</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K25" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L25" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M25" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N24" s="12" t="s">
+      <c r="N25" s="12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
         <v>46271</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B26" s="9">
         <v>380</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C26" s="9">
         <v>100</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D26" s="9">
         <v>430</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E26" s="9">
         <v>180</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F26" s="9">
         <v>0</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G26" s="9">
         <v>0</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H26" s="9">
         <v>0</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="M26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N25" s="12" t="s">
+      <c r="N26" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
         <v>46272</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B27" s="9">
         <v>330</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C27" s="9">
         <v>110</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D27" s="9">
         <v>200</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E27" s="9">
         <v>0</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F27" s="9">
         <v>200</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G27" s="9">
         <v>4</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H27" s="9">
         <v>50</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="M27" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N26" s="13" t="s">
+      <c r="N27" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
         <v>46273</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B28" s="9">
         <v>350</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C28" s="9">
         <v>80</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D28" s="9">
         <v>240</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E28" s="9">
         <v>80</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F28" s="9">
         <v>450</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G28" s="9">
         <v>7</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H28" s="9">
         <v>0</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L28" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M28" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N27" s="12" t="s">
+      <c r="N28" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+    <row r="29" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
         <v>46274</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B29" s="9">
         <v>310</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C29" s="9">
         <v>80</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D29" s="9">
         <v>180</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E29" s="9">
         <v>110</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F29" s="9">
         <v>450</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G29" s="9">
         <v>7</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H29" s="9">
         <v>0</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N28" s="12" t="s">
+      <c r="N29" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+    <row r="30" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
         <v>46275</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B30" s="9">
         <v>280</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C30" s="9">
         <v>110</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D30" s="9">
         <v>490</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E30" s="9">
         <v>210</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F30" s="9">
         <v>0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G30" s="9">
         <v>0</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H30" s="9">
         <v>0</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="K30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="M30" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N29" s="12" t="s">
+      <c r="N30" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+    <row r="31" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
         <v>46276</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B31" s="9">
         <v>310</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C31" s="9">
         <v>90</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D31" s="9">
         <v>210</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E31" s="9">
         <v>390</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F31" s="9">
         <v>0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G31" s="9">
         <v>0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H31" s="9">
         <v>0</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
         <v>440</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="K31" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N30" s="12" t="s">
+      <c r="N31" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
         <v>46277</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B32" s="9">
         <v>380</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C32" s="9">
         <v>70</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D32" s="9">
         <v>450</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E32" s="9">
         <v>80</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F32" s="9">
         <v>0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G32" s="9">
         <v>0</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H32" s="9">
         <v>50</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K32" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L32" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="M32" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N31" s="12" t="s">
+      <c r="N32" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
         <v>46278</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B33" s="9">
         <v>410</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C33" s="9">
         <v>65</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D33" s="9">
         <v>510</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E33" s="9">
         <v>0</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F33" s="9">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G33" s="9">
         <v>0</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H33" s="9">
         <v>0</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
         <v>985</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
         <v>455</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="K33" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L33" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M32" s="11" t="s">
+      <c r="M33" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N32" s="12" t="s">
+      <c r="N33" s="12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
         <v>46279</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B34" s="9">
         <v>390</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C34" s="9">
         <v>70</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D34" s="9">
         <v>270</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E34" s="9">
         <v>80</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F34" s="9">
         <v>200</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G34" s="9">
         <v>4</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H34" s="9">
         <v>30</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="K34" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L34" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M33" s="11" t="s">
+      <c r="M34" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N33" s="12" t="s">
+      <c r="N34" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
         <v>46280</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B35" s="9">
         <v>470</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C35" s="9">
         <v>80</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D35" s="9">
         <v>310</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E35" s="9">
         <v>130</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F35" s="9">
         <v>250</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G35" s="9">
         <v>5</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H35" s="9">
         <v>0</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
         <v>1240</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="K35" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L35" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M34" s="11" t="s">
+      <c r="M35" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N34" s="12" t="s">
+      <c r="N35" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
         <v>46281</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B36" s="9">
         <v>510</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C36" s="9">
         <v>70</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D36" s="9">
         <v>200</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E36" s="9">
         <v>0</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F36" s="9">
         <v>350</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G36" s="9">
         <v>7</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H36" s="9">
         <v>0</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="K36" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L36" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M35" s="11" t="s">
+      <c r="M36" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N35" s="12" t="s">
+      <c r="N36" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
         <v>46282</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B37" s="9">
         <v>480</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C37" s="9">
         <v>80</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D37" s="9">
         <v>310</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E37" s="9">
         <v>30</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F37" s="9">
         <v>200</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G37" s="9">
         <v>4</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H37" s="9">
         <v>80</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="K37" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L37" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M36" s="11" t="s">
+      <c r="M37" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N36" s="12" t="s">
+      <c r="N37" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
+    <row r="38" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
         <v>46283</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B38" s="9">
         <v>380</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C38" s="9">
         <v>110</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D38" s="9">
         <v>420</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E38" s="9">
         <v>0</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F38" s="9">
         <v>250</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G38" s="9">
         <v>5</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H38" s="9">
         <v>120</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
         <v>1280</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="K38" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L38" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M37" s="11" t="s">
+      <c r="M38" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N37" s="12" t="s">
+      <c r="N38" s="12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
         <v>46284</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B39" s="9">
         <v>430</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C39" s="9">
         <v>150</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D39" s="9">
         <v>320</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E39" s="9">
         <v>110</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F39" s="9">
         <v>0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G39" s="9">
         <v>0</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H39" s="9">
         <v>50</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="K39" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M38" s="11" t="s">
+      <c r="M39" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N38" s="12" t="s">
+      <c r="N39" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
         <v>46285</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B40" s="9">
         <v>370</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C40" s="9">
         <v>110</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D40" s="9">
         <v>540</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E40" s="9">
         <v>370</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F40" s="9">
         <v>0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G40" s="9">
         <v>0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H40" s="9">
         <v>130</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
         <v>1520</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J40" s="10">
         <v>380</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="K40" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L40" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M39" s="11" t="s">
+      <c r="M40" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N39" s="12" t="s">
+      <c r="N40" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
         <v>46286</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B41" s="9">
         <v>310</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C41" s="9">
         <v>150</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D41" s="9">
         <v>230</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E41" s="9">
         <v>0</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F41" s="9">
         <v>200</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G41" s="9">
         <v>4</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H41" s="9">
         <v>50</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="K41" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L41" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M40" s="11" t="s">
+      <c r="M41" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N40" s="12" t="s">
+      <c r="N41" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
         <v>46287</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B42" s="9">
         <v>480</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C42" s="9">
         <v>120</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D42" s="9">
         <v>180</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E42" s="9">
         <v>0</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F42" s="9">
         <v>450</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G42" s="9">
         <v>7</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H42" s="9">
         <v>0</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
         <v>1230</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="K42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L42" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M41" s="11" t="s">
+      <c r="M42" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N41" s="12" t="s">
+      <c r="N42" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A42" s="8">
+    <row r="43" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
         <v>46288</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B43" s="9">
         <v>320</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C43" s="9">
         <v>90</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D43" s="9">
         <v>360</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E43" s="9">
         <v>290</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F43" s="9">
         <v>300</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G43" s="9">
         <v>6</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H43" s="9">
         <v>0</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
         <v>1360</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K43" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L43" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M43" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N42" s="12" t="s">
+      <c r="N43" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
+    <row r="44" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
         <v>46289</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B44" s="9">
         <v>360</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C44" s="9">
         <v>110</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D44" s="9">
         <v>410</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E44" s="9">
         <v>90</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F44" s="9">
         <v>150</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G44" s="9">
         <v>3</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H44" s="9">
         <v>70</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
         <v>1190</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="K44" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L44" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M43" s="11" t="s">
+      <c r="M44" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N43" s="12" t="s">
+      <c r="N44" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
         <v>46290</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B45" s="9">
         <v>350</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C45" s="9">
         <v>130</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D45" s="9">
         <v>350</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E45" s="9">
         <v>130</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F45" s="9">
         <v>200</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G45" s="9">
         <v>4</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H45" s="9">
         <v>90</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
         <v>1250</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="K45" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L45" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M44" s="11" t="s">
+      <c r="M45" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N44" s="12" t="s">
+      <c r="N45" s="12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
         <v>46291</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B46" s="9">
         <v>120</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C46" s="9">
         <v>130</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D46" s="9">
         <v>240</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E46" s="9">
         <v>0</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F46" s="9">
         <v>100</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G46" s="9">
         <v>2</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H46" s="9">
         <v>0</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
         <v>590</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="K46" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L46" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M45" s="11" t="s">
+      <c r="M46" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N45" s="12" t="s">
+      <c r="N46" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
         <v>46292</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B47" s="9">
         <v>30</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C47" s="9">
         <v>0</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D47" s="9">
         <v>0</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E47" s="9">
         <v>0</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F47" s="9">
         <v>0</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G47" s="9">
         <v>0</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H47" s="9">
         <v>80</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
         <v>1330</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K47" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L47" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M46" s="11" t="s">
+      <c r="M47" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N46" s="12" t="s">
+      <c r="N47" s="12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
         <v>46293</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B48" s="9">
         <v>240</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C48" s="9">
         <v>120</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D48" s="9">
         <v>0</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E48" s="9">
         <v>0</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F48" s="9">
         <v>0</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G48" s="9">
         <v>0</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H48" s="9">
         <v>110</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
         <v>470</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
         <v>970</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K48" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L48" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M47" s="11" t="s">
+      <c r="M48" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="12" t="s">
+      <c r="N48" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
         <v>46294</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B49" s="9">
         <v>450</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C49" s="9">
         <v>180</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D49" s="9">
         <v>0</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E49" s="9">
         <v>0</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F49" s="9">
         <v>0</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G49" s="9">
         <v>0</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H49" s="9">
         <v>160</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
         <v>650</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K49" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L49" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M48" s="11" t="s">
+      <c r="M49" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N48" s="12" t="s">
+      <c r="N49" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
         <v>46295</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B50" s="9">
         <v>550</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C50" s="9">
         <v>190</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D50" s="9">
         <v>0</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E50" s="9">
         <v>0</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F50" s="9">
         <v>0</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G50" s="9">
         <v>0</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H50" s="9">
         <v>180</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
         <v>520</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K50" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L50" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M49" s="11" t="s">
+      <c r="M50" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N49" s="12" t="s">
+      <c r="N50" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
         <v>46296</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B51" s="9">
         <v>460</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C51" s="9">
         <v>180</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D51" s="9">
         <v>0</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E51" s="9">
         <v>0</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F51" s="9">
         <v>0</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G51" s="9">
         <v>0</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H51" s="9">
         <v>160</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
         <v>640</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K51" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L51" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M50" s="11" t="s">
+      <c r="M51" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N50" s="12" t="s">
+      <c r="N51" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
         <v>46297</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B52" s="9">
         <v>480</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C52" s="9">
         <v>220</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D52" s="9">
         <v>120</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E52" s="9">
         <v>50</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F52" s="9">
         <v>0</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G52" s="9">
         <v>0</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H52" s="9">
         <v>180</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K52" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L52" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M51" s="11" t="s">
+      <c r="M52" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="N51" s="12" t="s">
+      <c r="N52" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
         <v>46298</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B53" s="9">
         <v>370</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C53" s="9">
         <v>170</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D53" s="9">
         <v>250</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E53" s="9">
         <v>80</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F53" s="9">
         <v>0</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G53" s="9">
         <v>0</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H53" s="9">
         <v>150</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K53" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L53" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M52" s="11" t="s">
+      <c r="M53" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N52" s="12" t="s">
+      <c r="N53" s="12" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
-        <v>46299</v>
-      </c>
-      <c r="B53" s="9">
-        <v>430</v>
-      </c>
-      <c r="C53" s="9">
-        <v>180</v>
-      </c>
-      <c r="D53" s="9">
-        <v>320</v>
-      </c>
-      <c r="E53" s="9">
-        <v>120</v>
-      </c>
-      <c r="F53" s="9">
-        <v>0</v>
-      </c>
-      <c r="G53" s="9">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9">
-        <v>100</v>
-      </c>
-      <c r="I53" s="10">
-        <f t="shared" si="0"/>
-        <v>1150</v>
-      </c>
-      <c r="J53" s="10">
-        <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N53" s="12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="B54" s="9">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C54" s="9">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="D54" s="9">
-        <v>210</v>
+        <v>320</v>
       </c>
       <c r="E54" s="9">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F54" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G54" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="I54" s="10">
         <f t="shared" si="0"/>
@@ -3371,107 +3350,155 @@
         <v>290</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N54" s="12" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B55" s="9">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="C55" s="9">
         <v>150</v>
       </c>
       <c r="D55" s="9">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E55" s="9">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="F55" s="9">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G55" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H55" s="9">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I55" s="10">
         <f t="shared" si="0"/>
-        <v>1270</v>
+        <v>1150</v>
       </c>
       <c r="J55" s="10">
         <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="9">
+        <v>360</v>
+      </c>
+      <c r="C56" s="9">
+        <v>150</v>
+      </c>
+      <c r="D56" s="9">
+        <v>240</v>
+      </c>
+      <c r="E56" s="9">
+        <v>120</v>
+      </c>
+      <c r="F56" s="9">
+        <v>350</v>
+      </c>
+      <c r="G56" s="9">
+        <v>7</v>
+      </c>
+      <c r="H56" s="9">
+        <v>50</v>
+      </c>
+      <c r="I56" s="10">
+        <f t="shared" si="0"/>
+        <v>1270</v>
+      </c>
+      <c r="J56" s="10">
+        <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K56" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L55" s="11" t="s">
+      <c r="L56" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="M55" s="11" t="s">
+      <c r="M56" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N55" s="12" t="s">
+      <c r="N56" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="9">
+        <v>310</v>
+      </c>
+      <c r="C57" s="9">
+        <v>160</v>
+      </c>
+      <c r="D57" s="9">
+        <v>350</v>
+      </c>
+      <c r="E57" s="9">
+        <v>100</v>
+      </c>
+      <c r="F57" s="9">
+        <v>350</v>
+      </c>
+      <c r="G57" s="9">
+        <v>7</v>
+      </c>
+      <c r="H57" s="9">
+        <v>70</v>
+      </c>
+      <c r="I57" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
+        <v>100</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
@@ -3659,11 +3686,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" ref="I66:I129" si="2">IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" ref="J66:J129" si="3">IF(I66="","",1440-I66)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3681,11 +3708,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I67:I130" si="2">IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J67:J130" si="3">IF(I67="","",1440-I67)</f>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -5067,11 +5094,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" ref="I130:I193" si="4">IF(SUM(B130:F130,H130)=0,"",SUM(B130:F130,H130))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" ref="J130:J193" si="5">IF(I130="","",1440-I130)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -5089,11 +5116,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I131:I194" si="4">IF(SUM(B131:F131,H131)=0,"",SUM(B131:F131,H131))</f>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J131:J194" si="5">IF(I131="","",1440-I131)</f>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -6475,11 +6502,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" ref="I194:I257" si="6">IF(SUM(B194:F194,H194)=0,"",SUM(B194:F194,H194))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" ref="J194:J257" si="7">IF(I194="","",1440-I194)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6497,11 +6524,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I195:I258" si="6">IF(SUM(B195:F195,H195)=0,"",SUM(B195:F195,H195))</f>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J195:J258" si="7">IF(I195="","",1440-I195)</f>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -7883,11 +7910,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" ref="I258:I321" si="8">IF(SUM(B258:F258,H258)=0,"",SUM(B258:F258,H258))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" ref="J258:J321" si="9">IF(I258="","",1440-I258)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7905,11 +7932,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I259:I322" si="8">IF(SUM(B259:F259,H259)=0,"",SUM(B259:F259,H259))</f>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J259:J322" si="9">IF(I259="","",1440-I259)</f>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -9291,11 +9318,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" ref="I322:I385" si="10">IF(SUM(B322:F322,H322)=0,"",SUM(B322:F322,H322))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" ref="J322:J385" si="11">IF(I322="","",1440-I322)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -9313,11 +9340,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I323:I386" si="10">IF(SUM(B323:F323,H323)=0,"",SUM(B323:F323,H323))</f>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J323:J386" si="11">IF(I323="","",1440-I323)</f>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -10699,11 +10726,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" ref="I386:I397" si="12">IF(SUM(B386:F386,H386)=0,"",SUM(B386:F386,H386))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" ref="J386:J397" si="13">IF(I386="","",1440-I386)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10721,11 +10748,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I387:I398" si="12">IF(SUM(B387:F387,H387)=0,"",SUM(B387:F387,H387))</f>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J387:J398" si="13">IF(I387="","",1440-I387)</f>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10953,6 +10980,28 @@
       <c r="M397" s="11"/>
       <c r="N397" s="12"/>
     </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A398" s="8"/>
+      <c r="B398" s="9"/>
+      <c r="C398" s="9"/>
+      <c r="D398" s="9"/>
+      <c r="E398" s="9"/>
+      <c r="F398" s="9"/>
+      <c r="G398" s="9"/>
+      <c r="H398" s="9"/>
+      <c r="I398" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J398" s="10" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K398" s="11"/>
+      <c r="L398" s="11"/>
+      <c r="M398" s="11"/>
+      <c r="N398" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:N1"/>
@@ -10961,21 +11010,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J397">
+  <conditionalFormatting sqref="J6:J398">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K5:K397" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K398" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L5:L397" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L398" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M5:M397" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M398" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72F10EBA-E849-446B-81D3-6ACD0BD2F5FB}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7F9DE90-6B06-4069-AE0C-478AD59CF016}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -342,6 +342,9 @@
   <si>
     <t>Preparing for Midterm.</t>
   </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -513,9 +516,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1003,59 +1006,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="17">
         <v>12605028</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:14" ht="19.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="15" t="s">
         <v>100</v>
       </c>
       <c r="B4" s="14"/>
@@ -3501,26 +3504,49 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="9">
+        <v>410</v>
+      </c>
+      <c r="C58" s="9">
+        <v>180</v>
+      </c>
+      <c r="D58" s="9">
+        <v>410</v>
+      </c>
+      <c r="E58" s="9">
+        <v>220</v>
+      </c>
+      <c r="F58" s="9">
+        <v>200</v>
+      </c>
+      <c r="G58" s="9">
+        <v>5</v>
+      </c>
+      <c r="H58" s="9">
+        <v>60</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
+        <v>1480</v>
+      </c>
+      <c r="J58" s="10">
+        <v>120</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7F9DE90-6B06-4069-AE0C-478AD59CF016}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14384E8F-955B-4FF2-84B6-52A5A9C51094}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3520,7 +3520,7 @@
         <v>220</v>
       </c>
       <c r="F58" s="9">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G58" s="9">
         <v>5</v>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v>1480</v>
+        <v>1530</v>
       </c>
       <c r="J58" s="10">
         <v>120</v>
@@ -3549,26 +3549,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="9">
+        <v>300</v>
+      </c>
+      <c r="C59" s="9">
+        <v>120</v>
+      </c>
+      <c r="D59" s="9">
+        <v>300</v>
+      </c>
+      <c r="E59" s="9">
+        <v>100</v>
+      </c>
+      <c r="F59" s="9">
+        <v>200</v>
+      </c>
+      <c r="G59" s="9">
+        <v>4</v>
+      </c>
+      <c r="H59" s="9">
+        <v>100</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+        <v>320</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14384E8F-955B-4FF2-84B6-52A5A9C51094}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD1EBA93-7B2F-4F48-9843-C5535F991032}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3595,26 +3595,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="9">
+        <v>510</v>
+      </c>
+      <c r="C60" s="9">
+        <v>160</v>
+      </c>
+      <c r="D60" s="9">
+        <v>260</v>
+      </c>
+      <c r="E60" s="9">
+        <v>50</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>70</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD1EBA93-7B2F-4F48-9843-C5535F991032}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6334243-10EC-4870-B0F5-E646356FE52E}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3641,26 +3641,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="9">
+        <v>290</v>
+      </c>
+      <c r="C61" s="9">
+        <v>180</v>
+      </c>
+      <c r="D61" s="9">
+        <v>420</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>110</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6334243-10EC-4870-B0F5-E646356FE52E}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E13CCAA6-CFA6-40B2-95BF-0E863387E05C}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Giving networking midterm exam.</t>
   </si>
 </sst>
 </file>
@@ -3686,27 +3692,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
+    <row r="62" spans="1:14" ht="30.05" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="9">
+        <v>300</v>
+      </c>
+      <c r="C62" s="9">
+        <v>150</v>
+      </c>
+      <c r="D62" s="9">
+        <v>460</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>80</v>
+      </c>
+      <c r="I62" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E13CCAA6-CFA6-40B2-95BF-0E863387E05C}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A8B8784-6AB0-4768-8036-06B27AC332B4}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Giving networking midterm exam.</t>
+  </si>
+  <si>
+    <t>Giving C++ midterm exam.</t>
   </si>
 </sst>
 </file>
@@ -3739,26 +3742,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="9">
+        <v>320</v>
+      </c>
+      <c r="C63" s="9">
+        <v>180</v>
+      </c>
+      <c r="D63" s="9">
+        <v>520</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>90</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
+        <v>330</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A8B8784-6AB0-4768-8036-06B27AC332B4}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{388A29CD-F918-4554-921B-ABC7A69CC7D7}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Giving C++ midterm exam.</t>
+  </si>
+  <si>
+    <t>Giving DBMS midterm exam.</t>
   </si>
 </sst>
 </file>
@@ -3788,26 +3791,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+      <c r="A64" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="9">
+        <v>460</v>
+      </c>
+      <c r="C64" s="9">
+        <v>120</v>
+      </c>
+      <c r="D64" s="9">
+        <v>320</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>130</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{388A29CD-F918-4554-921B-ABC7A69CC7D7}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50427075-12C4-4A3D-89BB-92F9C25308CB}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3837,26 +3837,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="9">
+        <v>270</v>
+      </c>
+      <c r="C65" s="9">
+        <v>180</v>
+      </c>
+      <c r="D65" s="9">
+        <v>560</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>90</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>340</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50427075-12C4-4A3D-89BB-92F9C25308CB}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA33025-B888-4739-8B96-D92AB73A1053}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>Giving DBMS midterm exam.</t>
+  </si>
+  <si>
+    <t>Giving maths midterm.</t>
   </si>
 </sst>
 </file>
@@ -3883,26 +3886,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="9">
+        <v>340</v>
+      </c>
+      <c r="C66" s="9">
+        <v>210</v>
+      </c>
+      <c r="D66" s="9">
+        <v>410</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>120</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>360</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA33025-B888-4739-8B96-D92AB73A1053}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4416B757-9F14-41B0-B09A-CF053CBFD684}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>Giving maths midterm.</t>
+  </si>
+  <si>
+    <t>Giving English Midterm.</t>
   </si>
 </sst>
 </file>
@@ -3932,26 +3935,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="9">
+        <v>410</v>
+      </c>
+      <c r="C67" s="9">
+        <v>190</v>
+      </c>
+      <c r="D67" s="9">
+        <v>350</v>
+      </c>
+      <c r="E67" s="9">
+        <v>100</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>210</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" ref="I67:I130" si="2">IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" ref="J67:J130" si="3">IF(I67="","",1440-I67)</f>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>180</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4416B757-9F14-41B0-B09A-CF053CBFD684}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF772B3-C206-4CDD-A96E-425E206C6081}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Giving English Midterm.</t>
+  </si>
+  <si>
+    <t>Enjoying Sunday.</t>
   </si>
 </sst>
 </file>
@@ -3981,26 +3984,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="9">
+        <v>520</v>
+      </c>
+      <c r="C68" s="9">
+        <v>170</v>
+      </c>
+      <c r="D68" s="9">
+        <v>240</v>
+      </c>
+      <c r="E68" s="9">
+        <v>70</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>240</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>200</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF772B3-C206-4CDD-A96E-425E206C6081}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33782BF7-A146-41F5-B600-16C1057A0C49}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4030,26 +4030,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="9">
+        <v>540</v>
+      </c>
+      <c r="C69" s="9">
+        <v>110</v>
+      </c>
+      <c r="D69" s="9">
+        <v>180</v>
+      </c>
+      <c r="E69" s="9">
+        <v>30</v>
+      </c>
+      <c r="F69" s="9">
+        <v>150</v>
+      </c>
+      <c r="G69" s="9">
+        <v>3</v>
+      </c>
+      <c r="H69" s="9">
+        <v>200</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33782BF7-A146-41F5-B600-16C1057A0C49}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{800341AD-492D-46A3-B87C-A3C5E8562BC6}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4076,26 +4076,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="9">
+        <v>540</v>
+      </c>
+      <c r="C70" s="9">
+        <v>150</v>
+      </c>
+      <c r="D70" s="9">
+        <v>420</v>
+      </c>
+      <c r="E70" s="9">
+        <v>180</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>90</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>60</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{800341AD-492D-46A3-B87C-A3C5E8562BC6}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E9CA65B-C52A-4337-8388-4398F4F51EAD}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Enjoying Sunday.</t>
+  </si>
+  <si>
+    <t>Making C++ Project.</t>
   </si>
 </sst>
 </file>
@@ -4122,26 +4125,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="9">
+        <v>450</v>
+      </c>
+      <c r="C71" s="9">
+        <v>210</v>
+      </c>
+      <c r="D71" s="9">
+        <v>240</v>
+      </c>
+      <c r="E71" s="9">
+        <v>100</v>
+      </c>
+      <c r="F71" s="9">
+        <v>350</v>
+      </c>
+      <c r="G71" s="9">
+        <v>7</v>
+      </c>
+      <c r="H71" s="9">
+        <v>80</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="13_ncr:1_{C1109940-6713-4482-8049-792FEB7A3355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E9CA65B-C52A-4337-8388-4398F4F51EAD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -641,10 +641,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4171,26 +4167,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>540</v>
+      </c>
+      <c r="C72" s="9">
+        <v>180</v>
+      </c>
+      <c r="D72" s="9">
+        <v>180</v>
+      </c>
+      <c r="E72" s="9">
+        <v>120</v>
+      </c>
+      <c r="F72" s="9">
+        <v>150</v>
+      </c>
+      <c r="G72" s="9">
+        <v>3</v>
+      </c>
+      <c r="H72" s="9">
+        <v>110</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\OneDrive\Desktop\demo\cap776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49FBDF62-CB9C-4442-99E9-26286FF95A4B}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4213,26 +4213,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>540</v>
+      </c>
+      <c r="C73" s="9">
+        <v>120</v>
+      </c>
+      <c r="D73" s="9">
+        <v>200</v>
+      </c>
+      <c r="E73" s="9">
+        <v>150</v>
+      </c>
+      <c r="F73" s="9">
+        <v>200</v>
+      </c>
+      <c r="G73" s="9">
+        <v>4</v>
+      </c>
+      <c r="H73" s="9">
+        <v>120</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49FBDF62-CB9C-4442-99E9-26286FF95A4B}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{643C7D72-4146-47E1-BC55-2C783371FCCF}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -369,6 +369,9 @@
   <si>
     <t>Making C++ Project.</t>
   </si>
+  <si>
+    <t>Good day.</t>
+  </si>
 </sst>
 </file>
 
@@ -641,6 +644,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4259,26 +4266,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="9">
+        <v>480</v>
+      </c>
+      <c r="C74" s="9">
+        <v>150</v>
+      </c>
+      <c r="D74" s="9">
+        <v>90</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>420</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{643C7D72-4146-47E1-BC55-2C783371FCCF}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20875C36-CE34-40F8-80F2-D7379FDD1F26}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4312,26 +4312,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>540</v>
+      </c>
+      <c r="C75" s="9">
+        <v>160</v>
+      </c>
+      <c r="D75" s="9">
+        <v>300</v>
+      </c>
+      <c r="E75" s="9">
+        <v>120</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>300</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>20</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20875C36-CE34-40F8-80F2-D7379FDD1F26}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301F242C-4E75-4F71-986D-82F39178462F}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4358,26 +4358,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="9">
+        <v>390</v>
+      </c>
+      <c r="C76" s="9">
+        <v>210</v>
+      </c>
+      <c r="D76" s="9">
+        <v>240</v>
+      </c>
+      <c r="E76" s="9">
+        <v>90</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>240</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
+        <v>270</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{301F242C-4E75-4F71-986D-82F39178462F}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61220E10-E93F-4668-8566-B619E4F46CAB}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Good day.</t>
+  </si>
+  <si>
+    <t>Preparing for C++.</t>
   </si>
 </sst>
 </file>
@@ -4404,26 +4407,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="9">
+        <v>420</v>
+      </c>
+      <c r="C77" s="9">
+        <v>170</v>
+      </c>
+      <c r="D77" s="9">
+        <v>240</v>
+      </c>
+      <c r="E77" s="9">
+        <v>120</v>
+      </c>
+      <c r="F77" s="9">
+        <v>200</v>
+      </c>
+      <c r="G77" s="9">
+        <v>4</v>
+      </c>
+      <c r="H77" s="9">
+        <v>240</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61220E10-E93F-4668-8566-B619E4F46CAB}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701E784A-9361-45E0-B5DC-6C2C3EAFCA4B}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -373,7 +373,10 @@
     <t>Good day.</t>
   </si>
   <si>
-    <t>Preparing for C++.</t>
+    <t>Preparing for C++ viva.</t>
+  </si>
+  <si>
+    <t>Preparing for english CA.</t>
   </si>
 </sst>
 </file>
@@ -4453,26 +4456,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="9">
+        <v>390</v>
+      </c>
+      <c r="C78" s="9">
+        <v>160</v>
+      </c>
+      <c r="D78" s="9">
+        <v>300</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
+      <c r="F78" s="9">
+        <v>250</v>
+      </c>
+      <c r="G78" s="9">
+        <v>5</v>
+      </c>
+      <c r="H78" s="9">
+        <v>180</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>

--- a/12605028.xlsx
+++ b/12605028.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aed44bb9f3f589f6/Desktop/demo/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701E784A-9361-45E0-B5DC-6C2C3EAFCA4B}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{0A583C2C-61D7-4E42-88AA-428FDCDD25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D7AD73-F982-4A00-B541-0D20720A2099}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4502,48 +4502,96 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="9">
+        <v>420</v>
+      </c>
+      <c r="C79" s="9">
+        <v>190</v>
+      </c>
+      <c r="D79" s="9">
+        <v>240</v>
+      </c>
+      <c r="E79" s="9">
+        <v>60</v>
+      </c>
+      <c r="F79" s="9">
+        <v>200</v>
+      </c>
+      <c r="G79" s="9">
+        <v>4</v>
+      </c>
+      <c r="H79" s="9">
+        <v>210</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>120</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
+      <c r="A80" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B80" s="9">
+        <v>540</v>
+      </c>
+      <c r="C80" s="9">
+        <v>150</v>
+      </c>
+      <c r="D80" s="9">
+        <v>150</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0</v>
+      </c>
+      <c r="F80" s="9">
+        <v>250</v>
+      </c>
+      <c r="G80" s="9">
+        <v>5</v>
+      </c>
+      <c r="H80" s="9">
+        <v>300</v>
+      </c>
+      <c r="I80" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J80" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
